--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488052_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488052_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.134600000000001</v>
+        <v>9.0784</v>
       </c>
       <c r="E2" t="n">
         <v>6.9374</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1972</v>
+        <v>2.141</v>
       </c>
       <c r="G2" t="n">
         <v>9.769399999999999</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.8389</v>
       </c>
       <c r="T2" t="n">
         <v>-1.1745</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3918</v>
+        <v>0.3356</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0503</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1918</v>
+        <v>2.1357</v>
       </c>
       <c r="E3" t="n">
         <v>-0.3824</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5742</v>
+        <v>2.5181</v>
       </c>
       <c r="G3" t="n">
         <v>1.4776</v>
@@ -688,13 +688,13 @@
         <v>0.5947</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0192</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4257</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4066</v>
+        <v>0.3504</v>
       </c>
       <c r="V3" t="n">
         <v>0.337</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3132</v>
+        <v>0.6573</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3906</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0774</v>
+        <v>0.063</v>
       </c>
       <c r="G5" t="n">
         <v>1.9405</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7859</v>
+        <v>-1.4418</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.7322</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8499</v>
+        <v>-0.7096</v>
       </c>
       <c r="V5" t="n">
         <v>1.3479</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5606</v>
+        <v>-0.6449</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7433999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1828</v>
+        <v>0.0985</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6806</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1625</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0466</v>
+        <v>-0.0377</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6363</v>
+        <v>-1.5445</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.1576</v>
+        <v>0.7924</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5213</v>
+        <v>-2.3369</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1864</v>
+        <v>0.47</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6083</v>
+        <v>-2.0208</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5781</v>
+        <v>2.4907</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4263</v>
+        <v>1.6643</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3388</v>
+        <v>-0.3563</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9124</v>
+        <v>2.0206</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7601</v>
+        <v>-1.1943</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7304</v>
+        <v>-1.6645</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4905</v>
+        <v>0.4702</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.9378</v>
+        <v>1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>-9.3165</v>
+        <v>-0.3964</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.903</v>
+        <v>-1.9355</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8074</v>
+        <v>-1.6122</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7103</v>
+        <v>-0.3234</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2122</v>
+        <v>-1.6648</v>
       </c>
       <c r="W7" t="n">
-        <v>2.54</v>
+        <v>1.1367</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3278</v>
+        <v>-2.8015</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4636</v>
+        <v>-1.7734</v>
       </c>
       <c r="E8" t="n">
-        <v>1.098</v>
+        <v>-1.1941</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5615</v>
+        <v>-0.5793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.47</v>
+        <v>1.0608</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0208</v>
+        <v>0.5271</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4907</v>
+        <v>0.5337</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6643</v>
+        <v>0.9563</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3563</v>
+        <v>0.9887</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0206</v>
+        <v>-0.0324</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1943</v>
+        <v>0.1045</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6645</v>
+        <v>-0.4617</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4702</v>
+        <v>0.5661</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3964</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8545</v>
+        <v>-1.517</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3066</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.548</v>
+        <v>-0.7453</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6648</v>
+        <v>0.0704</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1367</v>
+        <v>0.6036</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8015</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2122</v>
+        <v>-2.4196</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2959</v>
+        <v>-4.565</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9163</v>
+        <v>2.1454</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0608</v>
+        <v>4.1864</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5271</v>
+        <v>2.6083</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5337</v>
+        <v>1.5781</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9563</v>
+        <v>3.4263</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9887</v>
+        <v>4.3388</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0324</v>
+        <v>-0.9124</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1045</v>
+        <v>0.7601</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4617</v>
+        <v>-1.7304</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5661</v>
+        <v>2.4905</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3876</v>
+        <v>-6.9378</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-9.3165</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9558</v>
+        <v>-0.8804</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8736</v>
+        <v>-1.2149</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0823</v>
+        <v>0.3345</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0704</v>
+        <v>1.2122</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6036</v>
+        <v>2.54</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5331</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7287</v>
+        <v>-2.8792</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6049</v>
+        <v>-5.4012</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8762</v>
+        <v>2.522</v>
       </c>
       <c r="G10" t="n">
         <v>3.1664</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.8387</v>
+        <v>-2.9891</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8095</v>
+        <v>-1.6058</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.0292</v>
+        <v>-1.3833</v>
       </c>
       <c r="V10" t="n">
         <v>2.0973</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7067</v>
+        <v>-5.2783</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4552</v>
+        <v>-3.2515</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2514</v>
+        <v>-2.0268</v>
       </c>
       <c r="G11" t="n">
         <v>-2.562</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.0329</v>
+        <v>-2.6045</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7361</v>
+        <v>-1.5324</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2968</v>
+        <v>-1.0721</v>
       </c>
       <c r="V11" t="n">
         <v>0.4828</v>
@@ -1348,10 +1348,10 @@
         <v>-1.160499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.705399999999999</v>
+        <v>-5.705499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5451</v>
+        <v>4.545</v>
       </c>
       <c r="G12" t="n">
         <v>20.3365</v>
@@ -1366,7 +1366,7 @@
         <v>20.5059</v>
       </c>
       <c r="K12" t="n">
-        <v>9.331200000000001</v>
+        <v>9.331199999999999</v>
       </c>
       <c r="L12" t="n">
         <v>11.1747</v>
@@ -1393,7 +1393,7 @@
         <v>-12.445</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.1942</v>
+        <v>-9.194199999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-3.2509</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.875500000000001</v>
+        <v>8.464700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1308</v>
+        <v>5.0289</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7447</v>
+        <v>3.4358</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5413</v>
@@ -1468,13 +1468,13 @@
         <v>3.568</v>
       </c>
       <c r="S13" t="n">
-        <v>3.52</v>
+        <v>3.1093</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1897</v>
+        <v>1.0878</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3303</v>
+        <v>2.0214</v>
       </c>
       <c r="V13" t="n">
         <v>6.3021</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1037</v>
+        <v>6.0871</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9612</v>
+        <v>3.7762</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1424</v>
+        <v>2.3109</v>
       </c>
       <c r="G14" t="n">
         <v>1.9106</v>
@@ -1546,13 +1546,13 @@
         <v>3.1716</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4706</v>
+        <v>2.454</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8849</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4006</v>
+        <v>1.5691</v>
       </c>
       <c r="V14" t="n">
         <v>0.5331</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0563</v>
+        <v>2.1846</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2538</v>
+        <v>-1.5594</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3101</v>
+        <v>3.744</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1772</v>
@@ -1624,13 +1624,13 @@
         <v>3.7662</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8063</v>
+        <v>1.9346</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4261</v>
+        <v>0.1205</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3802</v>
+        <v>1.8141</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3479</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5911999999999999</v>
+        <v>1.0268</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2133</v>
+        <v>0.1942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8045</v>
+        <v>0.8326</v>
       </c>
       <c r="G16" t="n">
         <v>0.3229</v>
@@ -1702,13 +1702,13 @@
         <v>0.1982</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0701</v>
+        <v>0.5056</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1248</v>
+        <v>0.2827</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1949</v>
+        <v>0.223</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2673</v>
+        <v>-0.1237</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2316</v>
+        <v>-1.4414</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9643</v>
+        <v>1.3177</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9457</v>
+        <v>-2.3588</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9626</v>
+        <v>-0.4075</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9832</v>
+        <v>-1.9513</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8332</v>
+        <v>-1.6273</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8417</v>
+        <v>0.3298</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9915</v>
+        <v>-1.957</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7789</v>
+        <v>-0.7315</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8042</v>
+        <v>-0.7372</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9747</v>
+        <v>0.0057</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9733</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9533</v>
+        <v>0.1845</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3718</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5815</v>
+        <v>0.2652</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6389</v>
+        <v>-0.2445</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8489</v>
+        <v>-1.8249</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2099</v>
+        <v>1.5804</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3588</v>
+        <v>-1.6349</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4075</v>
+        <v>-1.2658</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9513</v>
+        <v>-0.3691</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6273</v>
+        <v>-0.7073</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3298</v>
+        <v>-0.5984</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.957</v>
+        <v>-0.1089</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7315</v>
+        <v>-0.9276</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7372</v>
+        <v>-0.6674</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0057</v>
+        <v>-0.2602</v>
       </c>
       <c r="P18" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3307</v>
+        <v>0.2011</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4881</v>
+        <v>-0.1265</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1574</v>
+        <v>0.3276</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1881</v>
+        <v>-1.1869</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4361</v>
+        <v>-0.1946</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2481</v>
+        <v>-0.9923</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6349</v>
+        <v>-1.9457</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2658</v>
+        <v>-0.9626</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3691</v>
+        <v>-0.9832</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7073</v>
+        <v>1.8332</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5984</v>
+        <v>0.8417</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1089</v>
+        <v>0.9915</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9276</v>
+        <v>-3.7789</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6674</v>
+        <v>-1.8042</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2602</v>
+        <v>-1.9747</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1805</v>
+        <v>2.9733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7425</v>
+        <v>2.4991</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7377</v>
+        <v>0.9456</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0048</v>
+        <v>1.5535</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7851</v>
+        <v>-3.7081</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7783</v>
+        <v>-1.9821</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0068</v>
+        <v>-1.726</v>
       </c>
       <c r="G21" t="n">
         <v>-3.138</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1219</v>
+        <v>2.1989</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5823</v>
+        <v>1.3786</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5395</v>
+        <v>0.8203</v>
       </c>
       <c r="V21" t="n">
         <v>-3.9583</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.65</v>
+        <v>-4.2086</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3949</v>
+        <v>-2.0893</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2551</v>
+        <v>-2.1193</v>
       </c>
       <c r="G22" t="n">
         <v>-4.302</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1011</v>
+        <v>-0.7955</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1762</v>
+        <v>0.312</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8275</v>
+        <v>-5.8079</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2993</v>
+        <v>-3.8086</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5282</v>
+        <v>-1.9993</v>
       </c>
       <c r="G23" t="n">
         <v>-7.0976</v>
@@ -2248,13 +2248,13 @@
         <v>3.1716</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5634</v>
+        <v>0.5829</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1251</v>
+        <v>-0.3842</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4382</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4737</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1604</v>
+        <v>1.839500000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.337900000000002</v>
+        <v>-3.337900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>4.498199999999999</v>
+        <v>5.1774</v>
       </c>
       <c r="G24" t="n">
         <v>-20.3365</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6989000000000001</v>
+        <v>-0.6989000000000005</v>
       </c>
       <c r="I24" t="n">
         <v>-19.6377</v>
@@ -2326,13 +2326,13 @@
         <v>24.7779</v>
       </c>
       <c r="S24" t="n">
-        <v>12.4451</v>
+        <v>13.1241</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2509</v>
+        <v>3.2508</v>
       </c>
       <c r="U24" t="n">
-        <v>9.194000000000001</v>
+        <v>9.873399999999998</v>
       </c>
       <c r="V24" t="n">
         <v>-3.8326</v>
